--- a/Thu_Kha_Thi/notebooks/ket_qua_tinh_huong/bang_tinh_huong.xlsx
+++ b/Thu_Kha_Thi/notebooks/ket_qua_tinh_huong/bang_tinh_huong.xlsx
@@ -477,7 +477,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Công thức bắt trước</t>
+          <t>Công thức bắt trước; tính trên cả lỗ hổng CVSS dưới 8,0: 24 / 328 = 7,32%</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Công thức bắt trước</t>
+          <t>Ngưỡng vá khẩn cấp; tính trên cả lỗ hổng CVSS dưới 8,0: 14 / 328 = 4,27%</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1749,6 +1749,26 @@
           <t>Báo trước (tháng)</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Ngày gần nhất trở lại S từ 50</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Báo trước liên tục (tháng)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Số tháng rơi dưới 50 sau lần đầu</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Lần đầu đạt 50</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1781,6 +1801,24 @@
           <t>55</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>28/02/2022</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Trùng tháng EPSS đổi mô hình</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1813,16 +1851,34 @@
           <t>50</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>31/05/2023</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Tăng theo EPSS</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CVE-2019-5418</t>
+          <t>CVE-2019-9621</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rails Ruby on Rails</t>
+          <t>Synacor Zimbra Collaboration Suite (ZCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1843,18 +1899,36 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>49</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>31/05/2021</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Tháng đầu có điểm</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CVE-2019-9621</t>
+          <t>CVE-2019-5418</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Synacor Zimbra Collaboration Suite (ZCS)</t>
+          <t>Rails Ruby on Rails</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1875,6 +1949,24 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>49</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>31/05/2021</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Tháng đầu có điểm</t>
         </is>
       </c>
     </row>
@@ -1909,6 +2001,24 @@
           <t>47</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>31/03/2025</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>37</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Tăng theo EPSS</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1941,6 +2051,24 @@
           <t>45</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>31/12/2021</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Tháng đầu có điểm</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1973,6 +2101,24 @@
           <t>36</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>31/05/2021</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Tháng đầu có điểm</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2005,6 +2151,24 @@
           <t>35</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>31/03/2023</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Trùng tháng EPSS đổi mô hình</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2037,6 +2201,24 @@
           <t>35</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>28/02/2022</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Trùng tháng EPSS đổi mô hình</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2069,6 +2251,24 @@
           <t>28</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>31/03/2023</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Trùng tháng EPSS đổi mô hình</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2101,21 +2301,39 @@
           <t>27</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>28/02/2022</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Trùng tháng EPSS đổi mô hình</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CVE-2021-26086</t>
+          <t>CVE-2021-41277</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Atlassian Jira Server and Data Center</t>
+          <t>Metabase Metabase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5,3</t>
+          <t>7,5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2131,23 +2349,41 @@
       <c r="F13" t="inlineStr">
         <is>
           <t>19</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>29/02/2024</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Trùng tháng EPSS đổi mô hình</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CVE-2021-41277</t>
+          <t>CVE-2021-26086</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Metabase Metabase</t>
+          <t>Atlassian Jira Server and Data Center</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7,5</t>
+          <t>5,3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2163,6 +2399,24 @@
       <c r="F14" t="inlineStr">
         <is>
           <t>19</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>29/02/2024</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Trùng tháng EPSS đổi mô hình</t>
         </is>
       </c>
     </row>
@@ -2197,6 +2451,24 @@
           <t>18</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>31/12/2023</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Tăng theo EPSS</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2229,6 +2501,24 @@
           <t>16</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>28/02/2022</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Trùng tháng EPSS đổi mô hình</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2261,6 +2551,24 @@
           <t>15</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>28/02/2022</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Trùng tháng EPSS đổi mô hình</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2293,6 +2601,24 @@
           <t>14</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>31/03/2025</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Trùng tháng EPSS đổi mô hình</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2325,6 +2651,24 @@
           <t>13</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>31/03/2025</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Trùng tháng EPSS đổi mô hình</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2357,6 +2701,24 @@
           <t>9</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>30/04/2025</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Tăng theo EPSS</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2389,6 +2751,24 @@
           <t>6</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>31/03/2025</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Trùng tháng EPSS đổi mô hình</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2421,6 +2801,24 @@
           <t>6</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>30/09/2023</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Tăng theo EPSS</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2453,6 +2851,24 @@
           <t>4</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>31/12/2025</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Tăng theo EPSS</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2485,6 +2901,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>31/07/2023</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Tăng theo EPSS</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2515,6 +2949,24 @@
       <c r="F25" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>31/05/2025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Tăng theo EPSS</t>
         </is>
       </c>
     </row>

--- a/Thu_Kha_Thi/notebooks/ket_qua_tinh_huong/bang_tinh_huong.xlsx
+++ b/Thu_Kha_Thi/notebooks/ket_qua_tinh_huong/bang_tinh_huong.xlsx
@@ -1873,12 +1873,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CVE-2019-9621</t>
+          <t>CVE-2019-5418</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Synacor Zimbra Collaboration Suite (ZCS)</t>
+          <t>Rails Ruby on Rails</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CVE-2019-5418</t>
+          <t>CVE-2019-9621</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rails Ruby on Rails</t>
+          <t>Synacor Zimbra Collaboration Suite (ZCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2323,17 +2323,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CVE-2021-41277</t>
+          <t>CVE-2021-26086</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Metabase Metabase</t>
+          <t>Atlassian Jira Server and Data Center</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7,5</t>
+          <t>5,3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2373,17 +2373,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CVE-2021-26086</t>
+          <t>CVE-2021-41277</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Atlassian Jira Server and Data Center</t>
+          <t>Metabase Metabase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5,3</t>
+          <t>7,5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
